--- a/ksoft_old/docs/fields_details/BOM_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/BOM_Detail.xlsx
@@ -916,13 +916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24FAB48-50D3-496F-A97D-EF86F6369A3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6895B902-7D9E-4DB4-BE36-DA051EEB5BBE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5260349D-D5BF-4650-9EB5-1CBBA5D5C23B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE3127A-3053-44CC-AA1B-DA6F2CB111E7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE42835D-00D5-46BE-A66F-DC094ED4F987}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C50224A2-4091-4692-BB0E-D4855CD3DC11}"/>
 </file>
--- a/ksoft_old/docs/fields_details/BOM_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/BOM_Detail.xlsx
@@ -916,13 +916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6895B902-7D9E-4DB4-BE36-DA051EEB5BBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07244308-4D7C-40FA-AD8F-0F60EBD7BE11}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE3127A-3053-44CC-AA1B-DA6F2CB111E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21B1BDF-9DCC-430B-B8CB-2F95E94FAD81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C50224A2-4091-4692-BB0E-D4855CD3DC11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7FA6733-12BB-4CD1-85C1-F09802FA1122}"/>
 </file>
--- a/ksoft_old/docs/fields_details/BOM_Detail.xlsx
+++ b/ksoft_old/docs/fields_details/BOM_Detail.xlsx
@@ -916,13 +916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07244308-4D7C-40FA-AD8F-0F60EBD7BE11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24FAB48-50D3-496F-A97D-EF86F6369A3F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21B1BDF-9DCC-430B-B8CB-2F95E94FAD81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5260349D-D5BF-4650-9EB5-1CBBA5D5C23B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7FA6733-12BB-4CD1-85C1-F09802FA1122}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE42835D-00D5-46BE-A66F-DC094ED4F987}"/>
 </file>